--- a/public/sap-reporting/expansion-150-downloads/EXT-MM27-01.xlsx
+++ b/public/sap-reporting/expansion-150-downloads/EXT-MM27-01.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="R327b5f7b441149fb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R712de9e13c7342fe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="Rce0f93f9b1e54dc8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="Rc4976fa278bd46d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="Rc29b24055f3747b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R84814570402b4f9e"/>
   </x:sheets>
 </x:workbook>
 </file>
